--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0002T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>111.2151369856205</v>
+        <v>18.07245976016333</v>
       </c>
       <c r="D2" t="n">
-        <v>111.2151369856205</v>
+        <v>18.07245976016333</v>
       </c>
       <c r="E2" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F2" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>119.8788078634524</v>
+        <v>19.48030627781102</v>
       </c>
       <c r="D3" t="n">
-        <v>119.8788078634524</v>
+        <v>19.48030627781102</v>
       </c>
       <c r="E3" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F3" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>67.64965865047957</v>
+        <v>10.99306953070293</v>
       </c>
       <c r="D4" t="n">
-        <v>67.64965865047957</v>
+        <v>10.99306953070293</v>
       </c>
       <c r="E4" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F4" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>45.06272949184606</v>
+        <v>7.322693542424986</v>
       </c>
       <c r="D5" t="n">
-        <v>45.06272949184606</v>
+        <v>7.322693542424986</v>
       </c>
       <c r="E5" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F5" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>128.1976172081772</v>
+        <v>20.83211279632879</v>
       </c>
       <c r="D6" t="n">
-        <v>128.1976172081772</v>
+        <v>20.83211279632879</v>
       </c>
       <c r="E6" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F6" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>92.71085029902561</v>
+        <v>15.06551317359166</v>
       </c>
       <c r="D7" t="n">
-        <v>92.71085029902561</v>
+        <v>15.06551317359166</v>
       </c>
       <c r="E7" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F7" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>121.6812670408867</v>
+        <v>19.77320589414409</v>
       </c>
       <c r="D8" t="n">
-        <v>121.6812670408867</v>
+        <v>19.77320589414409</v>
       </c>
       <c r="E8" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F8" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.824662100579213</v>
+        <v>1.596507591344122</v>
       </c>
       <c r="D9" t="n">
-        <v>9.824662100579213</v>
+        <v>1.596507591344122</v>
       </c>
       <c r="E9" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F9" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.358243071338157</v>
+        <v>1.520714499092451</v>
       </c>
       <c r="D10" t="n">
-        <v>9.358243071338157</v>
+        <v>1.520714499092451</v>
       </c>
       <c r="E10" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F10" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>16.36217727852681</v>
+        <v>2.658853807760607</v>
       </c>
       <c r="D11" t="n">
-        <v>16.36217727852681</v>
+        <v>2.658853807760607</v>
       </c>
       <c r="E11" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F11" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>26.47792946352833</v>
+        <v>4.302663537823353</v>
       </c>
       <c r="D12" t="n">
-        <v>26.47792946352833</v>
+        <v>4.302663537823353</v>
       </c>
       <c r="E12" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F12" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.46615150367145</v>
+        <v>3.325749619346611</v>
       </c>
       <c r="D13" t="n">
-        <v>20.46615150367145</v>
+        <v>3.325749619346611</v>
       </c>
       <c r="E13" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F13" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>26.74198737514098</v>
+        <v>4.34557294846041</v>
       </c>
       <c r="D14" t="n">
-        <v>26.74198737514098</v>
+        <v>4.34557294846041</v>
       </c>
       <c r="E14" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F14" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>78.4128247599832</v>
+        <v>12.74208402349727</v>
       </c>
       <c r="D15" t="n">
-        <v>78.4128247599832</v>
+        <v>12.74208402349727</v>
       </c>
       <c r="E15" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F15" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>56.40569552630316</v>
+        <v>9.165925523024264</v>
       </c>
       <c r="D16" t="n">
-        <v>56.40569552630316</v>
+        <v>9.165925523024264</v>
       </c>
       <c r="E16" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F16" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>93.59978271370568</v>
+        <v>15.20996469097717</v>
       </c>
       <c r="D17" t="n">
-        <v>93.59978271370568</v>
+        <v>15.20996469097717</v>
       </c>
       <c r="E17" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F17" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>75.61840748526743</v>
+        <v>12.28799121635596</v>
       </c>
       <c r="D18" t="n">
-        <v>75.61840748526743</v>
+        <v>12.28799121635596</v>
       </c>
       <c r="E18" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="F18" t="n">
-        <v>40.68984051908423</v>
+        <v>6.612099084351186</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
